--- a/HTR-update-ML/ig/FRSectionFunctionalStatusLMCDAFHIR.xlsx
+++ b/HTR-update-ML/ig/FRSectionFunctionalStatusLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T12:45:48+00:00</t>
+    <t>2026-03-17T12:52:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
